--- a/data/trans_dic/IP2907_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2907_2023-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que durante sus primeros meses de vida recibiero unicamente lactancia artificial</t>
+          <t>Menores que durante sus primeros meses de vida recibiero unicamente lactancia artificial (tasa de respuesta: 98,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,54; 31,38</t>
+          <t>12,64; 30,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,2; 38,45</t>
+          <t>16,87; 37,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,86; 30,78</t>
+          <t>16,94; 30,59</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,09; 23,58</t>
+          <t>13,66; 23,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,6; 24,94</t>
+          <t>14,56; 24,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,34; 22,41</t>
+          <t>15,6; 22,69</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,36; 25,57</t>
+          <t>14,08; 24,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,63; 24,64</t>
+          <t>14,74; 25,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,02; 23,22</t>
+          <t>15,93; 23,69</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,43; 23,47</t>
+          <t>15,41; 24,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,56; 26,09</t>
+          <t>14,68; 26,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,9; 23,48</t>
+          <t>16,08; 23,44</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,75; 22,03</t>
+          <t>16,35; 21,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,02; 23,25</t>
+          <t>16,96; 23,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,55; 21,82</t>
+          <t>17,51; 21,83</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que durante sus primeros meses de vida recibiero unicamente lactancia artificial (tasa de respuesta: 98,6%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>9605</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11811</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>21417</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5940; 14224</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7715; 17109</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15707; 28365</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>28983</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>34883</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>63867</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>21582; 37153</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>26360; 45160</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>52883; 76938</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>32801</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>41293</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>74094</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>24155; 42488</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>31320; 53950</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>61162; 90975</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>46035</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>57920</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>103955</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>37045; 58182</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>43744; 80314</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>86574; 126222</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>117425</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>145907</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>263332</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>100877; 132963</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>125043; 172695</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>237069; 295702</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2907_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2907_2023-Edad-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,64; 30,26</t>
+          <t>12,4; 30,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,87; 37,42</t>
+          <t>16,61; 36,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,94; 30,59</t>
+          <t>17,09; 30,69</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,66; 23,51</t>
+          <t>13,86; 23,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,56; 24,94</t>
+          <t>14,96; 25,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,6; 22,69</t>
+          <t>15,71; 22,71</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,08; 24,77</t>
+          <t>14,14; 24,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,74; 25,39</t>
+          <t>14,5; 25,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,93; 23,69</t>
+          <t>15,83; 23,03</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,41; 24,2</t>
+          <t>15,31; 23,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,68; 26,95</t>
+          <t>14,41; 26,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,08; 23,44</t>
+          <t>16,24; 23,46</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,35; 21,55</t>
+          <t>16,22; 21,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,96; 23,42</t>
+          <t>17,17; 23,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,51; 21,83</t>
+          <t>17,44; 21,46</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5940; 14224</t>
+          <t>5828; 14327</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7715; 17109</t>
+          <t>7594; 16751</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15707; 28365</t>
+          <t>15845; 28459</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21582; 37153</t>
+          <t>21898; 37737</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26360; 45160</t>
+          <t>27083; 45255</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52883; 76938</t>
+          <t>53263; 76995</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24155; 42488</t>
+          <t>24255; 42242</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31320; 53950</t>
+          <t>30817; 54153</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>61162; 90975</t>
+          <t>60774; 88445</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37045; 58182</t>
+          <t>36818; 57682</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43744; 80314</t>
+          <t>42935; 78172</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86574; 126222</t>
+          <t>87444; 126343</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>100877; 132963</t>
+          <t>100103; 135554</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>125043; 172695</t>
+          <t>126570; 171111</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>237069; 295702</t>
+          <t>236214; 290681</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2907_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2907_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,4; 30,48</t>
+          <t>15,48; 35,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,61; 36,64</t>
+          <t>13,58; 31,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,09; 30,69</t>
+          <t>16,31; 30,14</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,86; 23,88</t>
+          <t>13,91; 24,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,96; 25,0</t>
+          <t>13,64; 22,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,71; 22,71</t>
+          <t>15,03; 21,94</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,14; 24,63</t>
+          <t>15,12; 25,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,5; 25,49</t>
+          <t>14,78; 25,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,83; 23,03</t>
+          <t>16,51; 23,97</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,31; 23,99</t>
+          <t>14,14; 24,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,41; 26,23</t>
+          <t>15,0; 23,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,24; 23,46</t>
+          <t>15,75; 22,53</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,22; 21,97</t>
+          <t>16,43; 22,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,17; 23,21</t>
+          <t>16,83; 22,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,44; 21,46</t>
+          <t>17,38; 21,55</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9605</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11811</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21417</t>
+          <t>18118</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5828; 14327</t>
+          <t>5854; 13434</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7594; 16751</t>
+          <t>5841; 13613</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15845; 28459</t>
+          <t>13186; 24360</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>50</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>28983</t>
+          <t>29283</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>34883</t>
+          <t>25585</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63867</t>
+          <t>54868</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21898; 37737</t>
+          <t>21740; 37796</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27083; 45255</t>
+          <t>19674; 32705</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53263; 76995</t>
+          <t>45188; 65957</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>44</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32801</t>
+          <t>39667</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41293</t>
+          <t>34052</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74094</t>
+          <t>73719</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24255; 42242</t>
+          <t>30258; 50343</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30817; 54153</t>
+          <t>25593; 44882</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60774; 88445</t>
+          <t>61622; 89460</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>67</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>46035</t>
+          <t>52605</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>57920</t>
+          <t>47644</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>103955</t>
+          <t>100248</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36818; 57682</t>
+          <t>40335; 69274</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42935; 78172</t>
+          <t>36698; 58400</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87444; 126343</t>
+          <t>83489; 119390</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>178</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>117425</t>
+          <t>130749</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>145907</t>
+          <t>116205</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>263332</t>
+          <t>246954</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>100103; 135554</t>
+          <t>111678; 150256</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>126570; 171111</t>
+          <t>101842; 133829</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>236214; 290681</t>
+          <t>223274; 276884</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2907_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2907_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que durante sus primeros meses de vida recibiero unicamente lactancia artificial (tasa de respuesta: 98,6%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>24,32%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>20,74%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>22,42%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>15,48; 35,53</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>13,58; 31,65</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16,31; 30,14</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>18,73%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>17,73%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>18,25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>13,91; 24,18</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>13,64; 22,67</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15,03; 21,94</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>19,82%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>19,67%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19,75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>15,12; 25,16</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>14,78; 25,93</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>16,51; 23,97</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>18,44%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>19,47%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18,91%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>14,14; 24,28</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>15,0; 23,87</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>15,75; 22,53</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>19,24%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>19,2%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>19,22%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>16,43; 22,11</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>16,83; 22,12</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>17,38; 21,55</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.2431808334998596</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.2074447538358256</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.2241615493146591</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>9195</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>8924</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>18118</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.1548142940911899</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.1357911323844628</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.1631357155027783</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>5854; 13434</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5841; 13613</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>13186; 24360</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.3553117189886409</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.3164649692747502</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.3013899379252203</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.1873485477266122</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1773184056032749</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1825338932297073</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>29283</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>25585</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>54868</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.1390902850123797</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.1363537375373172</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.1503294645069464</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>21740; 37796</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>19674; 32705</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>45188; 65957</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.2418181078984813</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.2266660720688052</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.2194236730071033</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.1982104094918738</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1967106635826452</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1975148217967267</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>39667</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>34052</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>73719</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.1511952307830692</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.1478440514035788</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.1651044788744202</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>30258; 50343</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>25593; 44882</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>61622; 89460</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.2515560393830885</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.2592773575775314</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.2396895696443892</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1843548759421956</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1947131364257353</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.189136735692382</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>52605</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>47644</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>100248</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.1413550620014768</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.1499808970712371</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.1575171628858678</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>40335; 69274</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>36698; 58400</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>83489; 119390</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.242772399690842</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.2386703341271872</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.2252512579023785</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.1923965303494996</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.1920418396847021</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1922294667789481</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>130749</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>116205</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>246954</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.1643337802569707</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.1683063272908316</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.1737970923602891</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>111678; 150256</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>101842; 133829</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>223274; 276884</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.221101438407431</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.2211683531009249</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.2155273301388264</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que durante sus primeros meses de vida recibiero unicamente lactancia artificial (tasa de respuesta: 98,6%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>9195</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>8924</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>18118</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>5854</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>5841</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>13186</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>13434</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>13613</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>24360</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>29283</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>25585</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>54868</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>21740</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>19674</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>45188</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>37796</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>32705</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>65957</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>39667</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>34052</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>73719</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>30258</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>25593</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>61622</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>50343</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>44882</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>89460</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>52605</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>47644</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>100248</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>40335</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>36698</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>83489</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>69274</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>58400</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>119390</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>179</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>178</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>130749</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>116205</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>246954</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>111678</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>101842</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>223274</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>150256</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>133829</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>276884</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>